--- a/template.xlsx
+++ b/template.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>音閱百寶箱</t>
+          <t>校訂E</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>3年級全部、4甲</t>
+          <t>1年級全部、2甲</t>
         </is>
       </c>
     </row>

--- a/template.xlsx
+++ b/template.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班級" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教師" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配課" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科目節數" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="場地" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="場地" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科目節數" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年段時段" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本土語分組" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>只要填 4 張表：①班級 ②教師 ③配課 ④確認科目節數。其餘分頁多數用預設即可。</t>
+          <t>只要填 4 張表：①班級（含導師，導師只填這裡）②教師（科任行政）③配課 ④確認科目節數。其餘分頁多數用預設即可。</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -860,50 +860,40 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>導師班級(導師填)</t>
+          <t>每週節數上限(留空=預設)</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>每週節數上限(留空=預設)</t>
+          <t>減課節數</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>減課節數</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
           <t>備註</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>上限預設：導師16／科任20／組長9／主任3／鐘點依聘。超鐘點與缺額由系統自動計算顯示。</t>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>導師免填！系統自動從「班級」分頁帶入（身份=導師、上限預設16、減課0）。此頁只填：科任／組長／主任／鐘點，以及「有減課或上限異動的導師」（加列即覆蓋預設）。上限預設：導師16／科任20／組長9／主任3。</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>王導師</t>
+          <t>張科任</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>導師</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>1甲</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
+          <t>科任</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>範例列</t>
         </is>
@@ -912,18 +902,18 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>張科任</t>
+          <t>陳組長</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>科任</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
+          <t>組長</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>範例列</t>
         </is>
@@ -932,20 +922,20 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>陳組長</t>
+          <t>王導師</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>組長</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>範例列</t>
+          <t>導師</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>範例：導師有減課才需要加列，其他導師免填</t>
         </is>
       </c>
     </row>
@@ -960,10 +950,10 @@
           <t>鐘點教師</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>缺額配課用，請保留</t>
         </is>
@@ -1082,6 +1072,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>場地名稱</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>同時段可容納班數</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>本土語徵用順位(選填)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>「原班教室」代表各班自己的教室，容量不用管。科目分頁的場地下拉會自動帶出本表名稱。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>原班教室</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>自然教室</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>音樂教室</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>電腦教室</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>操場</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>英語教室</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>圖書室</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>視聽教室</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1838,139 +1961,6 @@
       <formula1>"上午優先,2+1分兩天,兩節連堂,不排第4/5節,全年級同時段,"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>場地名稱</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>同時段可容納班數</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>本土語徵用順位(選填)</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>「原班教室」代表各班自己的教室，容量不用管。科目分頁的場地下拉會自動帶出本表名稱。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>原班教室</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>自然教室</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>音樂教室</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>電腦教室</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>操場</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>英語教室</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>圖書室</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>視聽教室</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/template.xlsx
+++ b/template.xlsx
@@ -11,9 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="學校基本資料" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班級" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教師" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配課" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="場地" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科目節數" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="場地" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科目節數" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配課" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年段時段" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本土語分組" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>只要填 4 張表：①班級（含導師，導師只填這裡）②教師（科任行政）③配課 ④確認科目節數。其餘分頁多數用預設即可。</t>
+          <t>填寫順序＝分頁順序：①班級（含導師，導師只填這裡）②教師（科任行政）③場地 ④科目節數（確認/修改）⑤配課 ⑥其餘分頁多數用預設即可。</t>
         </is>
       </c>
     </row>
@@ -975,103 +975,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>教師姓名</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>科目</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>任教班級</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>一列一組配課，同一位老師可多列。任教班級：「全部」／「3年級全部」／「3甲、3乙」。導師課免填（自動帶入）；導師課若因減課/超鐘點改他人任教，在此明列即覆蓋預設。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>張科任</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>音樂</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>全部</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>張科任</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>校訂E</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>5年級全部、6年級全部</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>陳組長</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>體育</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>1年級全部、2甲</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=科目節數!$A$2:$A$40</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1199,7 +1102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1959,6 +1862,103 @@
     </dataValidation>
     <dataValidation sqref="J2:J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"上午優先,2+1分兩天,兩節連堂,不排第4/5節,全年級同時段,"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>教師姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>科目</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>任教班級</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>一列一組配課，同一位老師可多列。任教班級：「全部」／「3年級全部」／「3甲、3乙」。導師課免填（自動帶入）；導師課若因減課/超鐘點改他人任教，在此明列即覆蓋預設。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>張科任</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>音樂</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>張科任</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>校訂E</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>5年級全部、6年級全部</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>陳組長</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>體育</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>1年級全部、2甲</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=科目節數!$A$2:$A$40</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/template.xlsx
+++ b/template.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B24"/>
+  <dimension ref="B2:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="2" max="2"/>
@@ -653,6 +653,20 @@
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">　＊比在 Excel 裡對 16~60 班 × 18 科的大矩陣快得多，也不會漏</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>【標題有 ▾ 的欄位＝下拉選單】Excel 的下拉箭頭要點到儲存格才會出現（Excel 本身限制），</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　看到 ▾ 就表示該欄可以下拉選、也可以直接打字。</t>
         </is>
       </c>
     </row>
@@ -748,7 +762,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>年級</t>
+          <t>年級 ▾</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -758,7 +772,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>有資源班學生(選填)</t>
+          <t>有資源班學生(選填) ▾</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
@@ -855,7 +869,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>身份</t>
+          <t>身份 ▾</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -1161,17 +1175,17 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>場地</t>
+          <t>場地 ▾</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>導師課</t>
+          <t>導師課 ▾</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>特殊規則</t>
+          <t>特殊規則 ▾</t>
         </is>
       </c>
       <c r="L1" s="7" t="inlineStr">
@@ -1890,7 +1904,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>科目</t>
+          <t>科目 ▾</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
@@ -2890,12 +2904,12 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>星期</t>
+          <t>星期 ▾</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>節次</t>
+          <t>節次 ▾</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -2910,7 +2924,7 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>教室</t>
+          <t>教室 ▾</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
